--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>פו פייטרס Caught In The Echo</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a9%d7%a8-%d7%9b%d7%94%d7%9f-%d7%9b%d7%95%d7%9c%d7%9d-%d7%92%d7%a0%d7%91%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-22</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אושר כהן שר דינמיקה זוגית לא בריאה, כמעט ממכרת בשיר פופ ים־תיכוני  שמשלב בין רגש גולמי, דרמה קולית והפקה עכשווית בשיר המתאר מערכת יחסים רעילה בגיל צעיר ליבת השיר היא מערכת יחסים סוערת שמבוססת על משיכה–דחייה: מצד אחד: "אני אוהב</v>
+        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אושר כהן – כולם גנבים</v>
+        <v>פו פייטרס Caught In The Echo</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%95-%d7%a4%d7%99%d7%99%d7%98%d7%a8%d7%a1-caught-in-the-echo/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אנחנו במרחק של בערך חודש מהוצאת האלבום החדש של פו פייטרס Foo Fighters, שנקרא  Your Favorite Toy, ודייב גרול והלהקה משתפים בסינגל השני – Caught In The Echo. לא היו לי בדיוק ציפיות בשמיים משיר חדש של פו פייטרס  עם</v>
+        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פו פייטרס Caught In The Echo</v>
+        <v>רועי שילה – הפרחים גבוהים עליסה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a2%d7%99-%d7%a9%d7%99%d7%9c%d7%94-%d7%94%d7%a4%d7%a8%d7%97%d7%99%d7%9d-%d7%92%d7%91%d7%95%d7%94%d7%99%d7%9d-%d7%a2%d7%9c%d7%99%d7%a1%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רועי שילה שר שיר קצר עדין, כמעט חלומי אבל עמוס במשמעות, שנע בין אהבה, התמסרות ואובדן גבולות זהות. “הפרחים גבוהים עליסה” – משפט  פשוט — אבל הוא טעון מאוד, שאומר: אנחנו נמצאים במרחב לא לגמרי מציאותי, אולי תודעתי או רגשי.</v>
+        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי שילה – הפרחים גבוהים עליסה</v>
+        <v>שירה זלוף – הפסקה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>נתלי – השטן לובשת פראדה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8%d7%94-%d7%96%d7%9c%d7%95%d7%a3-%d7%94%d7%a4%d7%a1%d7%a7%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%94%d7%a9%d7%98%d7%9f-%d7%9c%d7%95%d7%91%d7%a9%d7%aa-%d7%a4%d7%a8%d7%90%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שירה זלוף שרה בלדה אישית, כואבת וחשופה, שיר זיכרון שהופך לווידוי ומווידוי להאשמה. זה שיר על איך חוויות בית ספר מהעבר ממשיכות לחיות בתוך הגוף והנפש שנים קדימה. העבר לא נשאר בעבר – הוא פולש להווה, מפריע לשינה, מעורר תגובות</v>
+        <v>“השטן לובשת פראדה” של נתלי הוא פופ עכשווי שמצליח להיות גם קליט וגם טעון, ומה שמעניין בו  הוא הפער בין המעטפת הזוהרת לבין תוכן רגשי כבד, כמעט קיומי. שם השיר כמובן מהדהד את The Devil Wears Prada, אבל כאן “פראדה”</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירה זלוף – הפסקה</v>
+        <v>נתלי – השטן לובשת פראדה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתלי – השטן לובשת פראדה</v>
+        <v>אודיה – שיר לממ"ד</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%9c%d7%99-%d7%94%d7%a9%d7%98%d7%9f-%d7%9c%d7%95%d7%91%d7%a9%d7%aa-%d7%a4%d7%a8%d7%90%d7%93%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99%d7%94-%d7%a9%d7%99%d7%a8-%d7%9c%d7%9e%d7%9e%d7%93/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>“השטן לובשת פראדה” של נתלי הוא פופ עכשווי שמצליח להיות גם קליט וגם טעון, ומה שמעניין בו  הוא הפער בין המעטפת הזוהרת לבין תוכן רגשי כבד, כמעט קיומי. שם השיר כמובן מהדהד את The Devil Wears Prada, אבל כאן “פראדה”</v>
+        <v>אודיה שרה שיר שהוא ניסיון מובהק ליצור שיר “של הדור” – כזה שמחבר שמות, סיטואציות וסלנג לכדי קולאז’ חברת, אבל בין הכוונה לייצר אמירה רחבה לבין הביצוע, נוצר פער לא קטן. השיר בנוי כרצף דמויות: ששון, אלינור, שלום, רוקי, אורי,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתלי – השטן לובשת פראדה</v>
+        <v>אודיה – שיר לממ"ד</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אודיה – שיר לממ"ד</v>
+        <v>ששון שאולוב – ציון</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99%d7%94-%d7%a9%d7%99%d7%a8-%d7%9c%d7%9e%d7%9e%d7%93/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a6%d7%99%d7%95%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אודיה שרה שיר שהוא ניסיון מובהק ליצור שיר “של הדור” – כזה שמחבר שמות, סיטואציות וסלנג לכדי קולאז’ חברת, אבל בין הכוונה לייצר אמירה רחבה לבין הביצוע, נוצר פער לא קטן. השיר בנוי כרצף דמויות: ששון, אלינור, שלום, רוקי, אורי,</v>
+        <v>"ציון" של אליעזר בוצר הוא לא “שיר מרגש” במובן הפשוט של המילה. זה טקסט פיוטי-רוחני-לאומי כמעט נבואי. הוא נע בין אהבה לציון (כישות כמעט נשית) אשמה, חטא, ותשובה, חיפוש גאולה אישית וקולקטיבית, שיר שיש בו כאב, אבל גם עוצמה ואש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אודיה – שיר לממ"ד</v>
+        <v>ששון שאולוב – ציון</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב – ציון</v>
+        <v>עדן חסון ומתן לוי – עושה שלום</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%a9%d7%95%d7%9f-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%a6%d7%99%d7%95%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%95%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a9%d7%9c%d7%95%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ציון" של אליעזר בוצר הוא לא “שיר מרגש” במובן הפשוט של המילה. זה טקסט פיוטי-רוחני-לאומי כמעט נבואי. הוא נע בין אהבה לציון (כישות כמעט נשית) אשמה, חטא, ותשובה, חיפוש גאולה אישית וקולקטיבית, שיר שיש בו כאב, אבל גם עוצמה ואש</v>
+        <v>השיר "עושה שלום" בביצוע של עדן חסון ומתן לוי הוא ניסיון לגעת במקום רוחני־רגשי רחב, כזה שמחבר בין תפילה יהודית, פופ עכשווי, ואווירה של נחמה אחרי משבר. זה שיר שמכוון גבוה, לשאלות של אמונה, תקווה ומשמעות, אבל עושה זאת דרך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב – ציון</v>
+        <v>עדן חסון ומתן לוי – עושה שלום</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן חסון ומתן לוי – עושה שלום</v>
+        <v>נועם צוריאלי – צאי כבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%97%d7%a1%d7%95%d7%9f-%d7%95%d7%9e%d7%aa%d7%9f-%d7%9c%d7%95%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a9%d7%9c%d7%95%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%9d-%d7%a6%d7%95%d7%a8%d7%99%d7%90%d7%9c%d7%99-%d7%a6%d7%90%d7%99-%d7%9b%d7%91%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "עושה שלום" בביצוע של עדן חסון ומתן לוי הוא ניסיון לגעת במקום רוחני־רגשי רחב, כזה שמחבר בין תפילה יהודית, פופ עכשווי, ואווירה של נחמה אחרי משבר. זה שיר שמכוון גבוה, לשאלות של אמונה, תקווה ומשמעות, אבל עושה זאת דרך</v>
+        <v>השיר "צאי כבר" של נועם צוריאלי הוא אחד מאותם שירים שבהם הדרמה הרגשית לא רק מתוארת – היא מתרחשת בזמן אמת. זה מונולוג מתפרק של אדם שנקרע בין רצון להיאחז לבין צורך להיפרד, והמבנה המוזיקלי (ראפ – פזמון מלודי בפלצט)</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן חסון ומתן לוי – עושה שלום</v>
+        <v>נועם צוריאלי – צאי כבר</v>
       </c>
     </row>
   </sheetData>
